--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3942,6 +3942,39 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C109" s="8" t="n">
+        <v>258608.8</v>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México · Frecuencia: Semanal · Unidad: Millones de dólares</t>
+          <t>Fuente: Banco de México (SIE) · Frecuencia: Semanal · Unidad: Millones de dólares</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F163" s="8" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F169" s="8" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F185" s="8" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F195" s="8" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F203" s="8" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F205" s="8" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F207" s="8" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F209" s="8" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F211" s="8" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F212" s="6" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F213" s="8" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F214" s="6" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F216" s="6" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F217" s="8" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F218" s="6" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F219" s="8" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F221" s="8" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F222" s="6" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F223" s="8" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F226" s="6" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F228" s="6" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F229" s="8" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F230" s="6" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F231" s="8" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F232" s="6" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F233" s="8" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F234" s="6" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F236" s="6" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F238" s="6" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F239" s="8" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F240" s="6" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F241" s="8" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F242" s="6" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F244" s="6" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F245" s="8" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F246" s="6" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F247" s="8" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F248" s="6" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F249" s="8" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F250" s="6" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F251" s="8" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F252" s="6" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F253" s="8" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F254" s="6" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F255" s="8" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F256" s="6" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F257" s="8" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F258" s="6" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F259" s="8" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F260" s="6" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F261" s="8" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F262" s="6" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F263" s="8" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F264" s="6" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F265" s="8" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F266" s="6" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F267" s="8" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F268" s="6" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F270" s="6" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F272" s="6" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F274" s="6" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F276" s="6" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F278" s="6" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F280" s="6" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F282" s="6" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F284" s="6" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F286" s="6" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F288" s="6" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F290" s="6" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F292" s="6" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F294" s="6" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F296" s="6" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="E298" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F298" s="6" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="E300" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F300" s="6" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="E302" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F302" s="6" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="E304" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F304" s="6" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="E306" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F306" s="6" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F308" s="6" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="E310" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F310" s="6" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F312" s="6" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F314" s="6" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="E316" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F316" s="6" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="E318" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F318" s="6" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="E320" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F320" s="6" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E322" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F322" s="6" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="E324" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F324" s="6" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="E326" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F326" s="6" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="E328" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F328" s="6" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="E330" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F330" s="6" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F332" s="6" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="E334" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F334" s="6" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="E336" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F336" s="6" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="E338" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F338" s="6" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="E340" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F340" s="6" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="E342" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F342" s="6" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="E344" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F344" s="6" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="E346" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F346" s="6" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E348" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F348" s="6" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="E350" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F350" s="6" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E352" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F352" s="6" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="E354" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F354" s="6" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="E356" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F356" s="6" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E358" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F358" s="6" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="E360" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F360" s="6" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="E362" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F362" s="6" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="E364" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F364" s="6" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="E366" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F366" s="6" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="E368" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F368" s="6" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="E370" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F370" s="6" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="E372" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F372" s="6" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="E374" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F374" s="6" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="E376" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F376" s="6" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E378" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F378" s="6" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E380" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F380" s="6" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="E382" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F382" s="6" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="E384" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F384" s="6" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="E386" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F386" s="6" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="E388" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F388" s="6" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E390" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F390" s="6" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="E392" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F392" s="6" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="E394" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F394" s="6" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="E396" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F396" s="6" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="E398" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F398" s="6" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="E400" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F400" s="6" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="E402" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F402" s="6" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="E404" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F404" s="6" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="E406" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F406" s="6" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="E408" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F408" s="6" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="E410" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F410" s="6" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E412" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F412" s="6" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="E414" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F414" s="6" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="E416" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F416" s="6" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F417" s="8" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="E418" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F418" s="6" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F419" s="8" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="E420" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F420" s="6" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F421" s="8" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="E422" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F422" s="6" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F423" s="8" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="E424" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F424" s="6" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F425" s="8" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="E426" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F426" s="6" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F427" s="8" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="E428" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F428" s="6" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F429" s="8" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="E430" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F430" s="6" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F431" s="8" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E432" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F432" s="6" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F433" s="8" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="E434" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F434" s="6" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="E436" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F436" s="6" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="E438" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F438" s="6" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="E440" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F440" s="6" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="E442" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F442" s="6" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="E444" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F444" s="6" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="E446" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F446" s="6" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="E448" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F448" s="6" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="E450" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F450" s="6" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="E452" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F452" s="6" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="E454" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F454" s="6" t="inlineStr">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="E456" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F456" s="6" t="inlineStr">

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G456"/>
+  <dimension ref="A1:G457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14521,6 +14521,37 @@
         </is>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B457" s="4" t="n"/>
+      <c r="C457" s="7" t="n">
+        <v>258564.1</v>
+      </c>
+      <c r="D457" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="E457" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México (SIE)</t>
+        </is>
+      </c>
+      <c r="F457" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+        </is>
+      </c>
+      <c r="G457" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México (SIE) · Frecuencia: Semanal · Unidad: Millones de dólares</t>
+          <t>Fuente: Banco de México · Frecuencia: Semanal · Unidad: Millones de dólares</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F163" s="8" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F169" s="8" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F185" s="8" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F195" s="8" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F203" s="8" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F205" s="8" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F207" s="8" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F209" s="8" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F211" s="8" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F212" s="6" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F213" s="8" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F214" s="6" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F216" s="6" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F217" s="8" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F218" s="6" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F219" s="8" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F221" s="8" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F222" s="6" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F223" s="8" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F226" s="6" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F228" s="6" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F229" s="8" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F230" s="6" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F231" s="8" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F232" s="6" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F233" s="8" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F234" s="6" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F236" s="6" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F238" s="6" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F239" s="8" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F240" s="6" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F241" s="8" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F242" s="6" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F244" s="6" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F245" s="8" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F246" s="6" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F247" s="8" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F248" s="6" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F249" s="8" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F250" s="6" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F251" s="8" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F252" s="6" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F253" s="8" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F254" s="6" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F255" s="8" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F256" s="6" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F257" s="8" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F258" s="6" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F259" s="8" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F260" s="6" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F261" s="8" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F262" s="6" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F263" s="8" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F264" s="6" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F265" s="8" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F266" s="6" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F267" s="8" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F268" s="6" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F270" s="6" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F272" s="6" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F274" s="6" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F276" s="6" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F278" s="6" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F280" s="6" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F282" s="6" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F284" s="6" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F286" s="6" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F288" s="6" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F290" s="6" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F292" s="6" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F294" s="6" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F296" s="6" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="E298" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F298" s="6" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="E300" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F300" s="6" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="E302" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F302" s="6" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="E304" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F304" s="6" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="E306" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F306" s="6" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F308" s="6" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="E310" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F310" s="6" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F312" s="6" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F314" s="6" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="E316" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F316" s="6" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="E318" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F318" s="6" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="E320" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F320" s="6" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E322" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F322" s="6" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="E324" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F324" s="6" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="E326" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F326" s="6" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="E328" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F328" s="6" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="E330" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F330" s="6" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F332" s="6" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="E334" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F334" s="6" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="E336" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F336" s="6" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="E338" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F338" s="6" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="E340" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F340" s="6" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="E342" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F342" s="6" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="E344" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F344" s="6" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="E346" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F346" s="6" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E348" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F348" s="6" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="E350" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F350" s="6" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E352" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F352" s="6" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="E354" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F354" s="6" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="E356" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F356" s="6" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E358" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F358" s="6" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="E360" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F360" s="6" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="E362" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F362" s="6" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="E364" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F364" s="6" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="E366" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F366" s="6" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="E368" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F368" s="6" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="E370" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F370" s="6" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="E372" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F372" s="6" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="E374" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F374" s="6" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="E376" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F376" s="6" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E378" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F378" s="6" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E380" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F380" s="6" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="E382" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F382" s="6" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="E384" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F384" s="6" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="E386" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F386" s="6" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="E388" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F388" s="6" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E390" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F390" s="6" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="E392" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F392" s="6" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="E394" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F394" s="6" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="E396" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F396" s="6" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="E398" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F398" s="6" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="E400" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F400" s="6" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="E402" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F402" s="6" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="E404" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F404" s="6" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="E406" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F406" s="6" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="E408" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F408" s="6" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="E410" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F410" s="6" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E412" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F412" s="6" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="E414" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F414" s="6" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="E416" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F416" s="6" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F417" s="8" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="E418" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F418" s="6" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F419" s="8" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="E420" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F420" s="6" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F421" s="8" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="E422" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F422" s="6" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F423" s="8" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="E424" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F424" s="6" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F425" s="8" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="E426" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F426" s="6" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F427" s="8" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="E428" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F428" s="6" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F429" s="8" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="E430" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F430" s="6" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F431" s="8" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E432" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F432" s="6" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F433" s="8" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="E434" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F434" s="6" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="E436" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F436" s="6" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="E438" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F438" s="6" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="E440" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F440" s="6" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="E442" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F442" s="6" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="E444" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F444" s="6" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="E446" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F446" s="6" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="E448" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F448" s="6" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="E450" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F450" s="6" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="E452" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F452" s="6" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="E454" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F454" s="6" t="inlineStr">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="E456" s="6" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F456" s="6" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="E457" s="8" t="inlineStr">
         <is>
-          <t>Banco de México (SIE)</t>
+          <t>Banco de México</t>
         </is>
       </c>
       <c r="F457" s="8" t="inlineStr">

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México · Frecuencia: Semanal · Unidad: Millones de dólares</t>
+          <t>Fuente: Banco de México (SIE) · Frecuencia: Semanal · Unidad: Millones de dólares</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F159" s="8" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F163" s="8" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F169" s="8" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F185" s="8" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F195" s="8" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F203" s="8" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F205" s="8" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F207" s="8" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F209" s="8" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F211" s="8" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F212" s="6" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F213" s="8" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F214" s="6" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F216" s="6" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F217" s="8" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F218" s="6" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F219" s="8" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F221" s="8" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F222" s="6" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F223" s="8" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F226" s="6" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F228" s="6" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F229" s="8" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F230" s="6" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F231" s="8" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F232" s="6" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F233" s="8" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F234" s="6" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F236" s="6" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F238" s="6" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F239" s="8" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F240" s="6" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F241" s="8" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F242" s="6" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F244" s="6" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F245" s="8" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F246" s="6" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F247" s="8" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F248" s="6" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F249" s="8" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F250" s="6" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F251" s="8" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F252" s="6" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F253" s="8" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F254" s="6" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F255" s="8" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F256" s="6" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F257" s="8" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F258" s="6" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F259" s="8" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F260" s="6" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F261" s="8" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F262" s="6" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F263" s="8" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="E264" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F264" s="6" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F265" s="8" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F266" s="6" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F267" s="8" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F268" s="6" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F270" s="6" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F272" s="6" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F274" s="6" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F276" s="6" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F278" s="6" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F280" s="6" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F282" s="6" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E284" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F284" s="6" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F286" s="6" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="E288" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F288" s="6" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F290" s="6" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F292" s="6" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F294" s="6" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F296" s="6" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="E298" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F298" s="6" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="E300" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F300" s="6" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="E302" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F302" s="6" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="E304" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F304" s="6" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="E306" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F306" s="6" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="E308" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F308" s="6" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="E310" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F310" s="6" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F312" s="6" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F314" s="6" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="E316" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F316" s="6" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="E318" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F318" s="6" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="E320" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F320" s="6" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E322" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F322" s="6" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="E324" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F324" s="6" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="E326" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F326" s="6" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="E328" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F328" s="6" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="E330" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F330" s="6" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F332" s="6" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="E334" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F334" s="6" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="E336" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F336" s="6" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="E338" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F338" s="6" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="E340" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F340" s="6" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="E342" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F342" s="6" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="E344" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F344" s="6" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="E346" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F346" s="6" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E348" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F348" s="6" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="E350" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F350" s="6" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E352" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F352" s="6" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="E354" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F354" s="6" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="E356" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F356" s="6" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E358" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F358" s="6" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="E360" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F360" s="6" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="E362" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F362" s="6" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="E364" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F364" s="6" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="E366" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F366" s="6" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="E368" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F368" s="6" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="E370" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F370" s="6" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="E372" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F372" s="6" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="E374" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F374" s="6" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="E376" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F376" s="6" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E378" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F378" s="6" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E380" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F380" s="6" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="E382" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F382" s="6" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="E384" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F384" s="6" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="E386" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F386" s="6" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="E388" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F388" s="6" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E390" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F390" s="6" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="E392" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F392" s="6" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="E394" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F394" s="6" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="E396" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F396" s="6" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="E398" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F398" s="6" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="E400" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F400" s="6" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="E402" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F402" s="6" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="E404" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F404" s="6" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="E406" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F406" s="6" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="E408" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F408" s="6" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="E410" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F410" s="6" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E412" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F412" s="6" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="E414" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F414" s="6" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="E416" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F416" s="6" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F417" s="8" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="E418" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F418" s="6" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F419" s="8" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="E420" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F420" s="6" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F421" s="8" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="E422" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F422" s="6" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F423" s="8" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="E424" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F424" s="6" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F425" s="8" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="E426" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F426" s="6" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F427" s="8" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="E428" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F428" s="6" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F429" s="8" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="E430" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F430" s="6" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F431" s="8" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E432" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F432" s="6" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F433" s="8" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="E434" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F434" s="6" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="E436" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F436" s="6" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="E438" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F438" s="6" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="E440" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F440" s="6" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="E442" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F442" s="6" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="E444" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F444" s="6" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="E446" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F446" s="6" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="E448" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F448" s="6" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="E450" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F450" s="6" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="E452" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F452" s="6" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="E454" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F454" s="6" t="inlineStr">
@@ -14476,7 +14476,7 @@
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="E456" s="6" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F456" s="6" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="E457" s="8" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="F457" s="8" t="inlineStr">

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -510,7 +510,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/ · Fecha de publicación: —</t>
+          <t>URL del boletín / serie: https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf · Fecha de publicación: —</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J51" s="12" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J53" s="12" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J65" s="12" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J67" s="12" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J71" s="12" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J75" s="12" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J77" s="12" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J79" s="12" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J81" s="12" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J83" s="12" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J85" s="12" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J87" s="12" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J89" s="12" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J93" s="12" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J95" s="12" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J97" s="12" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J101" s="12" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J103" s="12" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J109" s="12" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J117" s="12" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J138" s="8" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J142" s="8" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J144" s="8" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J150" s="8" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J151" s="12" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J152" s="8" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J154" s="8" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J156" s="8" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J167" s="12" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J169" s="12" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J170" s="8" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J171" s="12" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J172" s="8" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J173" s="12" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J174" s="8" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J176" s="8" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J178" s="8" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J180" s="8" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J182" s="8" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J183" s="12" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="I184" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J184" s="8" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J185" s="12" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="I186" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J186" s="8" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J187" s="12" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="I188" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J188" s="8" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J189" s="12" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="I190" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J190" s="8" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J191" s="12" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="I192" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J192" s="8" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="I193" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J193" s="12" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="I194" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J194" s="8" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="I195" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J195" s="12" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="I196" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J196" s="8" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="I197" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J197" s="12" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="I198" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J198" s="8" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="I199" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J199" s="12" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I200" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J200" s="8" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="I201" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J201" s="12" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="I202" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J202" s="8" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="I203" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J203" s="12" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="I204" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J204" s="8" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="I205" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J205" s="12" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="I206" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J206" s="8" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I207" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J207" s="12" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="I208" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J208" s="8" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="I209" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J209" s="12" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="I210" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J210" s="8" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="I211" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J211" s="12" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="I212" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J212" s="8" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="I213" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J213" s="12" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="I214" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J214" s="8" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="I215" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J215" s="12" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="I216" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J216" s="8" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I217" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J217" s="12" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="I218" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J218" s="8" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="I219" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J219" s="12" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="I220" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J220" s="8" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="I221" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J221" s="12" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="I222" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J222" s="8" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I223" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J223" s="12" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="I224" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J224" s="8" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="I225" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J225" s="12" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I226" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J226" s="8" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I227" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J227" s="12" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="I228" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J228" s="8" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="I229" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J229" s="12" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="I230" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J230" s="8" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="I231" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J231" s="12" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I232" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J232" s="8" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="I233" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J233" s="12" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="I234" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J234" s="8" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="I235" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J235" s="12" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="I236" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J236" s="8" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="I237" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J237" s="12" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="I238" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J238" s="8" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="I239" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J239" s="12" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="I240" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J240" s="8" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="I241" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J241" s="12" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="I242" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J242" s="8" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="I243" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J243" s="12" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="I244" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J244" s="8" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="I245" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J245" s="12" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I246" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J246" s="8" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="I247" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J247" s="12" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="I248" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J248" s="8" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="I249" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J249" s="12" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="I250" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J250" s="8" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="I251" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J251" s="12" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="I252" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J252" s="8" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="I253" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J253" s="12" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="I254" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J254" s="8" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="I255" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J255" s="12" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="I256" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J256" s="8" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="I257" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J257" s="12" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="I258" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J258" s="8" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="I259" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J259" s="12" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="I260" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J260" s="8" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="I261" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J261" s="12" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="I262" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J262" s="8" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="I263" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J263" s="12" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="I264" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J264" s="8" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="I265" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J265" s="12" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="I266" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J266" s="8" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="I267" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J267" s="12" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="I268" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J268" s="8" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="I269" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J269" s="12" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="I270" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J270" s="8" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="I271" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J271" s="12" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="I272" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J272" s="8" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="I273" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J273" s="12" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I274" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J274" s="8" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="I275" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J275" s="12" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="I276" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J276" s="8" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="I277" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J277" s="12" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="I278" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J278" s="8" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="I279" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J279" s="12" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="I280" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J280" s="8" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="I281" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J281" s="12" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="I282" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J282" s="8" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="I283" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J283" s="12" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="I284" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J284" s="8" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="I285" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J285" s="12" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="I286" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J286" s="8" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="I287" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J287" s="12" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="I288" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J288" s="8" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="I289" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J289" s="12" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="I290" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J290" s="8" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="I291" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J291" s="12" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="I292" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J292" s="8" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="I293" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J293" s="12" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="I294" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J294" s="8" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="I295" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J295" s="12" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="I296" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J296" s="8" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="I297" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J297" s="12" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="I298" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J298" s="8" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="I299" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J299" s="12" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="I300" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J300" s="8" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="I301" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J301" s="12" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="I302" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J302" s="8" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="I303" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J303" s="12" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="I304" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J304" s="8" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="I305" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J305" s="12" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="I306" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J306" s="8" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="I307" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J307" s="12" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="I308" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J308" s="8" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="I309" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J309" s="12" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="I310" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J310" s="8" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="I311" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J311" s="12" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="I312" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J312" s="8" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="I313" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J313" s="12" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="I314" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J314" s="8" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="I315" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J315" s="12" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="I316" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J316" s="8" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="I317" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J317" s="12" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="I318" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J318" s="8" t="inlineStr">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="I319" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J319" s="12" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="I320" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J320" s="8" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="I321" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J321" s="12" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="I322" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J322" s="8" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="I323" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J323" s="12" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="I324" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J324" s="8" t="inlineStr">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="I325" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J325" s="12" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="I326" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J326" s="8" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="I327" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J327" s="12" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="I328" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J328" s="8" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="I329" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J329" s="12" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="I330" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J330" s="8" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="I331" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J331" s="12" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="I332" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J332" s="8" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="I333" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J333" s="12" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="I334" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J334" s="8" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="I335" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J335" s="12" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="I336" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J336" s="8" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="I337" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J337" s="12" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="I338" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J338" s="8" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="I339" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J339" s="12" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="I340" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J340" s="8" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="I341" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J341" s="12" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="I342" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J342" s="8" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="I343" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J343" s="12" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="I344" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J344" s="8" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="I345" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J345" s="12" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="I346" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J346" s="8" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="I347" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J347" s="12" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="I348" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J348" s="8" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="I349" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J349" s="12" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="I350" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J350" s="8" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="I351" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J351" s="12" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="I352" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J352" s="8" t="inlineStr">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="I353" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J353" s="12" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="I354" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J354" s="8" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="I355" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J355" s="12" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="I356" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J356" s="8" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="I357" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J357" s="12" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="I358" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J358" s="8" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="I359" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J359" s="12" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="I360" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J360" s="8" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="I361" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J361" s="12" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="I362" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J362" s="8" t="inlineStr">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="I363" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J363" s="12" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="I364" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J364" s="8" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="I365" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J365" s="12" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="I366" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J366" s="8" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="I367" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J367" s="12" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="I368" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J368" s="8" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="I369" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J369" s="12" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="I370" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J370" s="8" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="I371" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J371" s="12" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="I372" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J372" s="8" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="I373" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J373" s="12" t="inlineStr">
@@ -15107,7 +15107,7 @@
       </c>
       <c r="I374" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J374" s="8" t="inlineStr">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="I375" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J375" s="12" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="I376" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J376" s="8" t="inlineStr">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="I377" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J377" s="12" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I378" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J378" s="8" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="I379" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J379" s="12" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="I380" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J380" s="8" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="I381" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J381" s="12" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="I382" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J382" s="8" t="inlineStr">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="I383" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J383" s="12" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="I384" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J384" s="8" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="I385" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J385" s="12" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="I386" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J386" s="8" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="I387" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J387" s="12" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="I388" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J388" s="8" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="I389" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J389" s="12" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="I390" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J390" s="8" t="inlineStr">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="I391" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J391" s="12" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="I392" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J392" s="8" t="inlineStr">
@@ -15867,7 +15867,7 @@
       </c>
       <c r="I393" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J393" s="12" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="I394" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J394" s="8" t="inlineStr">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="I395" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J395" s="12" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="I396" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J396" s="8" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="I397" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J397" s="12" t="inlineStr">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="I398" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J398" s="8" t="inlineStr">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="I399" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J399" s="12" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="I400" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J400" s="8" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="I401" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J401" s="12" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="I402" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J402" s="8" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="I403" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J403" s="12" t="inlineStr">
@@ -16307,7 +16307,7 @@
       </c>
       <c r="I404" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J404" s="8" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="I405" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J405" s="12" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="I406" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J406" s="8" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="I407" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J407" s="12" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="I408" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J408" s="8" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="I409" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J409" s="12" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="I410" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J410" s="8" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="I411" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J411" s="12" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="I412" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J412" s="8" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="I413" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J413" s="12" t="inlineStr">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="I414" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J414" s="8" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="I415" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J415" s="12" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="I416" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J416" s="8" t="inlineStr">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="I417" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J417" s="12" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="I418" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J418" s="8" t="inlineStr">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="I419" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J419" s="12" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="I420" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J420" s="8" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="I421" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J421" s="12" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="I422" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J422" s="8" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="I423" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J423" s="12" t="inlineStr">
@@ -17107,7 +17107,7 @@
       </c>
       <c r="I424" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J424" s="8" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="I425" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J425" s="12" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="I426" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J426" s="8" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="I427" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J427" s="12" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="I428" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J428" s="8" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="I429" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J429" s="12" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="I430" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J430" s="8" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="I431" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J431" s="12" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="I432" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J432" s="8" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="I433" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J433" s="12" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="I434" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J434" s="8" t="inlineStr">
@@ -17547,7 +17547,7 @@
       </c>
       <c r="I435" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J435" s="12" t="inlineStr">
@@ -17587,7 +17587,7 @@
       </c>
       <c r="I436" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J436" s="8" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="I437" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J437" s="12" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="I438" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J438" s="8" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="I439" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J439" s="12" t="inlineStr">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="I440" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J440" s="8" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="I441" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J441" s="12" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="I442" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J442" s="8" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="I443" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J443" s="12" t="inlineStr">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="I444" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J444" s="8" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="I445" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J445" s="12" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="I446" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J446" s="8" t="inlineStr">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="I447" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J447" s="12" t="inlineStr">
@@ -18067,7 +18067,7 @@
       </c>
       <c r="I448" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J448" s="8" t="inlineStr">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="I449" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J449" s="12" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="I450" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J450" s="8" t="inlineStr">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="I451" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J451" s="12" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="I452" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J452" s="8" t="inlineStr">
@@ -18267,7 +18267,7 @@
       </c>
       <c r="I453" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J453" s="12" t="inlineStr">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="I454" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J454" s="8" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="I455" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J455" s="12" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="I456" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J456" s="8" t="inlineStr">
@@ -18427,7 +18427,7 @@
       </c>
       <c r="I457" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
         </is>
       </c>
       <c r="J457" s="12" t="inlineStr">

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -510,7 +510,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf · Fecha de publicación: —</t>
+          <t>URL del boletín / serie: https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html · Fecha de publicación: —</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J51" s="12" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J53" s="12" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J65" s="12" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J67" s="12" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J71" s="12" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J75" s="12" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J77" s="12" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J79" s="12" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J81" s="12" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J83" s="12" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J85" s="12" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J87" s="12" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J89" s="12" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="I90" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J91" s="12" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J93" s="12" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="I94" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J95" s="12" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="I96" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J97" s="12" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="I100" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J101" s="12" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J103" s="12" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="I108" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J109" s="12" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J117" s="12" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="I134" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="I136" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J136" s="8" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="I138" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J138" s="8" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="I140" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J140" s="8" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="I142" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J142" s="8" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J144" s="8" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="I146" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J146" s="8" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="I150" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J150" s="8" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J151" s="12" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="I152" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J152" s="8" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="I154" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J154" s="8" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="I156" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J156" s="8" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="I158" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J158" s="8" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J160" s="8" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J167" s="12" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="I168" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J168" s="8" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J169" s="12" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="I170" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J170" s="8" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J171" s="12" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J172" s="8" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J173" s="12" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J174" s="8" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J176" s="8" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J178" s="8" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J180" s="8" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J182" s="8" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J183" s="12" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="I184" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J184" s="8" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J185" s="12" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="I186" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J186" s="8" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J187" s="12" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="I188" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J188" s="8" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J189" s="12" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="I190" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J190" s="8" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J191" s="12" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="I192" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J192" s="8" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="I193" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J193" s="12" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="I194" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J194" s="8" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="I195" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J195" s="12" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="I196" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J196" s="8" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="I197" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J197" s="12" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="I198" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J198" s="8" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="I199" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J199" s="12" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I200" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J200" s="8" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="I201" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J201" s="12" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="I202" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J202" s="8" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="I203" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J203" s="12" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="I204" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J204" s="8" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="I205" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J205" s="12" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="I206" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J206" s="8" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I207" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J207" s="12" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="I208" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J208" s="8" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="I209" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J209" s="12" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="I210" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J210" s="8" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="I211" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J211" s="12" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="I212" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J212" s="8" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="I213" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J213" s="12" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="I214" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J214" s="8" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="I215" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J215" s="12" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="I216" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J216" s="8" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I217" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J217" s="12" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="I218" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J218" s="8" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="I219" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J219" s="12" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="I220" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J220" s="8" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="I221" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J221" s="12" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="I222" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J222" s="8" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="I223" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J223" s="12" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="I224" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J224" s="8" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="I225" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J225" s="12" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I226" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J226" s="8" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I227" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J227" s="12" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="I228" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J228" s="8" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="I229" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J229" s="12" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="I230" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J230" s="8" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="I231" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J231" s="12" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I232" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J232" s="8" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="I233" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J233" s="12" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="I234" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J234" s="8" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="I235" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J235" s="12" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="I236" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J236" s="8" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="I237" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J237" s="12" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="I238" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J238" s="8" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="I239" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J239" s="12" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="I240" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J240" s="8" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="I241" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J241" s="12" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="I242" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J242" s="8" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="I243" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J243" s="12" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="I244" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J244" s="8" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="I245" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J245" s="12" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="I246" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J246" s="8" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="I247" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J247" s="12" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="I248" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J248" s="8" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="I249" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J249" s="12" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="I250" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J250" s="8" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="I251" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J251" s="12" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="I252" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J252" s="8" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="I253" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J253" s="12" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="I254" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J254" s="8" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="I255" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J255" s="12" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="I256" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J256" s="8" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="I257" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J257" s="12" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="I258" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J258" s="8" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="I259" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J259" s="12" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="I260" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J260" s="8" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="I261" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J261" s="12" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="I262" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J262" s="8" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="I263" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J263" s="12" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="I264" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J264" s="8" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="I265" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J265" s="12" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="I266" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J266" s="8" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="I267" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J267" s="12" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="I268" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J268" s="8" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="I269" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J269" s="12" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="I270" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J270" s="8" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="I271" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J271" s="12" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="I272" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J272" s="8" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="I273" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J273" s="12" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I274" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J274" s="8" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="I275" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J275" s="12" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="I276" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J276" s="8" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="I277" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J277" s="12" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="I278" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J278" s="8" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="I279" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J279" s="12" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="I280" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J280" s="8" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="I281" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J281" s="12" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="I282" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J282" s="8" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="I283" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J283" s="12" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="I284" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J284" s="8" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="I285" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J285" s="12" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="I286" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J286" s="8" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="I287" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J287" s="12" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="I288" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J288" s="8" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="I289" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J289" s="12" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="I290" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J290" s="8" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="I291" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J291" s="12" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="I292" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J292" s="8" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="I293" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J293" s="12" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="I294" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J294" s="8" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="I295" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J295" s="12" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="I296" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J296" s="8" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="I297" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J297" s="12" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="I298" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J298" s="8" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="I299" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J299" s="12" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="I300" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J300" s="8" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="I301" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J301" s="12" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="I302" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J302" s="8" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="I303" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J303" s="12" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="I304" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J304" s="8" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="I305" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J305" s="12" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="I306" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J306" s="8" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="I307" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J307" s="12" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="I308" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J308" s="8" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="I309" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J309" s="12" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="I310" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J310" s="8" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="I311" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J311" s="12" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="I312" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J312" s="8" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="I313" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J313" s="12" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="I314" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J314" s="8" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="I315" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J315" s="12" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="I316" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J316" s="8" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="I317" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J317" s="12" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="I318" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J318" s="8" t="inlineStr">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="I319" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J319" s="12" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="I320" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J320" s="8" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="I321" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J321" s="12" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="I322" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J322" s="8" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="I323" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J323" s="12" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="I324" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J324" s="8" t="inlineStr">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="I325" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J325" s="12" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="I326" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J326" s="8" t="inlineStr">
@@ -13227,7 +13227,7 @@
       </c>
       <c r="I327" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J327" s="12" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="I328" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J328" s="8" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="I329" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J329" s="12" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="I330" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J330" s="8" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="I331" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J331" s="12" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="I332" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J332" s="8" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="I333" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J333" s="12" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="I334" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J334" s="8" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="I335" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J335" s="12" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="I336" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J336" s="8" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="I337" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J337" s="12" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="I338" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J338" s="8" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="I339" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J339" s="12" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="I340" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J340" s="8" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="I341" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J341" s="12" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="I342" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J342" s="8" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="I343" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J343" s="12" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="I344" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J344" s="8" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="I345" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J345" s="12" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="I346" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J346" s="8" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="I347" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J347" s="12" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="I348" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J348" s="8" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="I349" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J349" s="12" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="I350" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J350" s="8" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="I351" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J351" s="12" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="I352" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J352" s="8" t="inlineStr">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="I353" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J353" s="12" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="I354" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J354" s="8" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="I355" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J355" s="12" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="I356" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J356" s="8" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="I357" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J357" s="12" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="I358" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J358" s="8" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="I359" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J359" s="12" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="I360" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J360" s="8" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="I361" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J361" s="12" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="I362" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J362" s="8" t="inlineStr">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="I363" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J363" s="12" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="I364" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J364" s="8" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="I365" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J365" s="12" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="I366" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J366" s="8" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="I367" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J367" s="12" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="I368" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J368" s="8" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="I369" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J369" s="12" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="I370" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J370" s="8" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="I371" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J371" s="12" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="I372" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J372" s="8" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="I373" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J373" s="12" t="inlineStr">
@@ -15107,7 +15107,7 @@
       </c>
       <c r="I374" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J374" s="8" t="inlineStr">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="I375" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J375" s="12" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="I376" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J376" s="8" t="inlineStr">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="I377" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J377" s="12" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="I378" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J378" s="8" t="inlineStr">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="I379" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J379" s="12" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="I380" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J380" s="8" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="I381" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J381" s="12" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="I382" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J382" s="8" t="inlineStr">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="I383" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J383" s="12" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="I384" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J384" s="8" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="I385" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J385" s="12" t="inlineStr">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="I386" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J386" s="8" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="I387" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J387" s="12" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="I388" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J388" s="8" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="I389" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J389" s="12" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="I390" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J390" s="8" t="inlineStr">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="I391" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J391" s="12" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="I392" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J392" s="8" t="inlineStr">
@@ -15867,7 +15867,7 @@
       </c>
       <c r="I393" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J393" s="12" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="I394" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J394" s="8" t="inlineStr">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="I395" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J395" s="12" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="I396" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J396" s="8" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="I397" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J397" s="12" t="inlineStr">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="I398" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J398" s="8" t="inlineStr">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="I399" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J399" s="12" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="I400" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J400" s="8" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="I401" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J401" s="12" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="I402" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J402" s="8" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="I403" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J403" s="12" t="inlineStr">
@@ -16307,7 +16307,7 @@
       </c>
       <c r="I404" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J404" s="8" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="I405" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J405" s="12" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="I406" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J406" s="8" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="I407" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J407" s="12" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="I408" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J408" s="8" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="I409" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J409" s="12" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="I410" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J410" s="8" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="I411" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J411" s="12" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="I412" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J412" s="8" t="inlineStr">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="I413" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J413" s="12" t="inlineStr">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="I414" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J414" s="8" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="I415" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J415" s="12" t="inlineStr">
@@ -16787,7 +16787,7 @@
       </c>
       <c r="I416" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J416" s="8" t="inlineStr">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="I417" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J417" s="12" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="I418" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J418" s="8" t="inlineStr">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="I419" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J419" s="12" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="I420" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J420" s="8" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="I421" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J421" s="12" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="I422" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J422" s="8" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="I423" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J423" s="12" t="inlineStr">
@@ -17107,7 +17107,7 @@
       </c>
       <c r="I424" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J424" s="8" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="I425" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J425" s="12" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="I426" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J426" s="8" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="I427" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J427" s="12" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="I428" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J428" s="8" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="I429" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J429" s="12" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="I430" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J430" s="8" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="I431" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J431" s="12" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="I432" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J432" s="8" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="I433" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J433" s="12" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="I434" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J434" s="8" t="inlineStr">
@@ -17547,7 +17547,7 @@
       </c>
       <c r="I435" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J435" s="12" t="inlineStr">
@@ -17587,7 +17587,7 @@
       </c>
       <c r="I436" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J436" s="8" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="I437" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J437" s="12" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="I438" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J438" s="8" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="I439" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J439" s="12" t="inlineStr">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="I440" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J440" s="8" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="I441" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J441" s="12" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="I442" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J442" s="8" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="I443" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J443" s="12" t="inlineStr">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="I444" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J444" s="8" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="I445" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J445" s="12" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="I446" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J446" s="8" t="inlineStr">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="I447" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J447" s="12" t="inlineStr">
@@ -18067,7 +18067,7 @@
       </c>
       <c r="I448" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J448" s="8" t="inlineStr">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="I449" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J449" s="12" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="I450" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J450" s="8" t="inlineStr">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="I451" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J451" s="12" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="I452" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J452" s="8" t="inlineStr">
@@ -18267,7 +18267,7 @@
       </c>
       <c r="I453" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J453" s="12" t="inlineStr">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="I454" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J454" s="8" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="I455" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J455" s="12" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="I456" s="8" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J456" s="8" t="inlineStr">
@@ -18427,7 +18427,7 @@
       </c>
       <c r="I457" s="12" t="inlineStr">
         <is>
-          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/{CCBFCEE4-FB9B-F179-93C3-F376FBE5491F}.pdf</t>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
         </is>
       </c>
       <c r="J457" s="12" t="inlineStr">

--- a/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
+++ b/downloads/indicadores/RESERVAS/RESERVAS_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J457"/>
+  <dimension ref="A1:J458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18436,6 +18436,46 @@
         </is>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B458" s="4" t="n"/>
+      <c r="C458" s="5" t="n">
+        <v>258034.6</v>
+      </c>
+      <c r="D458" s="6" t="n">
+        <v>-529.5</v>
+      </c>
+      <c r="E458" s="6" t="n">
+        <v>5905</v>
+      </c>
+      <c r="F458" s="7" t="n">
+        <v>0.051206</v>
+      </c>
+      <c r="G458" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H458" s="8" t="inlineStr">
+        <is>
+          <t>Banco de México — SIE / Estado de cuenta semanal</t>
+        </is>
+      </c>
+      <c r="I458" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/estado-de-cuenta-semanal/estado-cuenta-semanal-reserva.html</t>
+        </is>
+      </c>
+      <c r="J458" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
